--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131078671</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131078683</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131078652</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131078671</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131078683</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131078652</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131078671</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131078683</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>131078652</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>133040256</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>133039949</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>133040013</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>133040365</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>133040256</v>
       </c>
       <c r="B5" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>133039949</v>
       </c>
       <c r="B6" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>133040013</v>
       </c>
       <c r="B7" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>133040365</v>
       </c>
       <c r="B8" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1454,6 +1454,548 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133945016</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>795274</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7255339</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133967871</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Granskog Ö om Igeltjärnsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>795271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7255303</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133945922</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Granskog Ö Igeltjärnsberget, Bergsviken, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>795196</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7255271</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133945697</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Granskog Ö om Igeltjärnsberget, Granskog Ö om Igeltjärnsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>795287</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7255328</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133967853</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granskog Ö om Igeltjärnsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>795271</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7255303</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -1459,7 +1459,7 @@
         <v>133945016</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>133945697</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131078671</v>
+        <v>133945922</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Granskog Ö Igeltjärnsberget, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795439</v>
+        <v>795196</v>
       </c>
       <c r="R2" t="n">
-        <v>7255502</v>
+        <v>7255271</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +745,19 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -784,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131078683</v>
+        <v>133967871</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,23 +814,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granskog Ö Igeltjärnsberget, Bergsviken, Nb</t>
+          <t>Granskog Ö om Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795301</v>
+        <v>795271</v>
       </c>
       <c r="R3" t="n">
-        <v>7255388</v>
+        <v>7255303</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +889,7 @@
         <v>131078652</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,62 +995,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133040256</v>
+        <v>131078671</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö Igeltjärnsberget, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795287</v>
+        <v>795439</v>
       </c>
       <c r="R5" t="n">
-        <v>7255260</v>
+        <v>7255502</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,62 +1104,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133039949</v>
+        <v>131078683</v>
       </c>
       <c r="B6" t="n">
-        <v>99140</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö Igeltjärnsberget, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>795301</v>
       </c>
       <c r="R6" t="n">
-        <v>7255375</v>
+        <v>7255388</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,17 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Åtskilliga plantor.</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,62 +1213,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133040013</v>
+        <v>133967853</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö om Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>795370</v>
+        <v>795271</v>
       </c>
       <c r="R7" t="n">
-        <v>7255468</v>
+        <v>7255303</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,12 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,59 +1322,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133040365</v>
+        <v>133945818</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>56706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>206046</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö om Igeltjärnsberget, Granskog Ö om Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>795231</v>
+        <v>795284</v>
       </c>
       <c r="R8" t="n">
-        <v>7255228</v>
+        <v>7255323</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1419,17 +1395,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Såg en planta, kan nog finnas fler.</t>
+          <t>20-25 cm stor...</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133945016</v>
+        <v>133039949</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>795274</v>
+        <v>795301</v>
       </c>
       <c r="R9" t="n">
-        <v>7255339</v>
+        <v>7255375</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,12 +1511,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Åtskilliga plantor.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,60 +1548,62 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133967871</v>
+        <v>133040013</v>
       </c>
       <c r="B10" t="n">
-        <v>58349</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskog Ö om Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795271</v>
+        <v>795370</v>
       </c>
       <c r="R10" t="n">
-        <v>7255303</v>
+        <v>7255468</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,12 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,53 +1659,62 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133945922</v>
+        <v>133040256</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskog Ö Igeltjärnsberget, Bergsviken, Nb</t>
+          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795196</v>
+        <v>795287</v>
       </c>
       <c r="R11" t="n">
-        <v>7255271</v>
+        <v>7255260</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,19 +1738,19 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1778,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133945697</v>
+        <v>133040365</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,12 +1800,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1823,17 +1815,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granskog Ö om Igeltjärnsberget, Granskog Ö om Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795287</v>
+        <v>795231</v>
       </c>
       <c r="R12" t="n">
-        <v>7255328</v>
+        <v>7255228</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,12 +1849,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Såg en planta, kan nog finnas fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,60 +1886,62 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133967853</v>
+        <v>133945016</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Granskog Ö om Igeltjärnsberget, Nb</t>
+          <t>Granskog Ö Igeltjärnsberget, Granskog Ö Igeltjärnsberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795271</v>
+        <v>795274</v>
       </c>
       <c r="R13" t="n">
-        <v>7255303</v>
+        <v>7255339</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1994,117 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133945697</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granskog Ö om Igeltjärnsberget, Granskog Ö om Igeltjärnsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>795287</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7255328</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5331-2026 artfynd.xlsx
+++ b/artfynd/A 5331-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133945922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133967871</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131078652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131078671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131078683</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133967853</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133945818</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133039949</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133040013</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133040256</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133040365</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133945016</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,8 +2170,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133945697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>